--- a/artfynd/A 16088-2026 artfynd.xlsx
+++ b/artfynd/A 16088-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132653601</v>
       </c>
       <c r="B2" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132653800</v>
       </c>
       <c r="B3" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>132653736</v>
       </c>
       <c r="B4" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>132653783</v>
       </c>
       <c r="B5" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>132654012</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16088-2026 artfynd.xlsx
+++ b/artfynd/A 16088-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132653601</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132653800</v>
+        <v>132653690</v>
       </c>
       <c r="B3" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482171</v>
+        <v>482158</v>
       </c>
       <c r="R3" t="n">
-        <v>6598558</v>
+        <v>6598583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132653736</v>
+        <v>132653783</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482158</v>
+        <v>482171</v>
       </c>
       <c r="R4" t="n">
-        <v>6598583</v>
+        <v>6598557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132653783</v>
+        <v>132653800</v>
       </c>
       <c r="B5" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>482171</v>
       </c>
       <c r="R5" t="n">
-        <v>6598557</v>
+        <v>6598558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,7 +1182,7 @@
         <v>132654012</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,6 +1302,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132914423</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>482413</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6598522</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16088-2026 artfynd.xlsx
+++ b/artfynd/A 16088-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132653601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132653690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132653783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132653800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132654012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,8 +1438,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132914423</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>